--- a/companies/broadcom/data/Financials.xlsx
+++ b/companies/broadcom/data/Financials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="20">
   <si>
     <t>期間</t>
   </si>
@@ -640,14 +640,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="21" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1">
         <v>2020</v>
@@ -682,8 +682,11 @@
       <c r="V1">
         <v>2025</v>
       </c>
+      <c r="Z1">
+        <v>2026</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -759,8 +762,20 @@
       <c r="Y2" t="s">
         <v>4</v>
       </c>
+      <c r="Z2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -836,8 +851,11 @@
       <c r="Y3">
         <v>18015</v>
       </c>
+      <c r="Z3">
+        <v>19311</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -911,8 +929,20 @@
       <c r="Y4">
         <f>Y3/X3</f>
       </c>
+      <c r="Z4">
+        <f>Z3/Y3</f>
+      </c>
+      <c r="AA4">
+        <f>AA3/Z3</f>
+      </c>
+      <c r="AB4">
+        <f>AB3/AA3</f>
+      </c>
+      <c r="AC4">
+        <f>AC3/AB3</f>
+      </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
@@ -980,8 +1010,20 @@
       <c r="Y5">
         <f>U3/Y3</f>
       </c>
+      <c r="Z5">
+        <f>V3/Z3</f>
+      </c>
+      <c r="AA5">
+        <f>W3/AA3</f>
+      </c>
+      <c r="AB5">
+        <f>X3/AB3</f>
+      </c>
+      <c r="AC5">
+        <f>Y3/AC3</f>
+      </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
@@ -1057,8 +1099,11 @@
       <c r="Y6">
         <v>12249</v>
       </c>
+      <c r="Z6">
+        <v>13157</v>
+      </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>9</v>
       </c>
@@ -1134,8 +1179,11 @@
       <c r="Y7">
         <f>Y6/Y$3</f>
       </c>
+      <c r="Z7">
+        <f>Z6/Z$3</f>
+      </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>7</v>
       </c>
@@ -1203,8 +1251,20 @@
       <c r="Y8">
         <f>Y6/U6</f>
       </c>
+      <c r="Z8">
+        <f>Z6/V6</f>
+      </c>
+      <c r="AA8">
+        <f>AA6/W6</f>
+      </c>
+      <c r="AB8">
+        <f>AB6/X6</f>
+      </c>
+      <c r="AC8">
+        <f>AC6/Y6</f>
+      </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>10</v>
       </c>
@@ -1280,8 +1340,11 @@
       <c r="Y9">
         <v>2981</v>
       </c>
+      <c r="Z9">
+        <v>2965</v>
+      </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>9</v>
       </c>
@@ -1357,8 +1420,20 @@
       <c r="Y10">
         <f>Y9/Y$3</f>
       </c>
+      <c r="Z10">
+        <f>Z9/Z$3</f>
+      </c>
+      <c r="AA10">
+        <f>AA9/AA$3</f>
+      </c>
+      <c r="AB10">
+        <f>AB9/AB$3</f>
+      </c>
+      <c r="AC10">
+        <f>AC9/AC$3</f>
+      </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>11</v>
       </c>
@@ -1434,8 +1509,11 @@
       <c r="Y11">
         <v>1107</v>
       </c>
+      <c r="Z11">
+        <v>1019</v>
+      </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>9</v>
       </c>
@@ -1511,8 +1589,20 @@
       <c r="Y12">
         <f>Y11/Y$3</f>
       </c>
+      <c r="Z12">
+        <f>Z11/Z$3</f>
+      </c>
+      <c r="AA12">
+        <f>AA11/AA$3</f>
+      </c>
+      <c r="AB12">
+        <f>AB11/AB$3</f>
+      </c>
+      <c r="AC12">
+        <f>AC11/AC$3</f>
+      </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>12</v>
       </c>
@@ -1588,8 +1678,11 @@
       <c r="Y13">
         <v>4088</v>
       </c>
+      <c r="Z13">
+        <v>3984</v>
+      </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>9</v>
       </c>
@@ -1665,8 +1758,20 @@
       <c r="Y14">
         <f>Y13/Y$3</f>
       </c>
+      <c r="Z14">
+        <f>Z13/Z$3</f>
+      </c>
+      <c r="AA14">
+        <f>AA13/AA$3</f>
+      </c>
+      <c r="AB14">
+        <f>AB13/AB$3</f>
+      </c>
+      <c r="AC14">
+        <f>AC13/AC$3</f>
+      </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>7</v>
       </c>
@@ -1734,8 +1839,20 @@
       <c r="Y15">
         <f>Y13/U13</f>
       </c>
+      <c r="Z15">
+        <f>Z13/V13</f>
+      </c>
+      <c r="AA15">
+        <f>AA13/W13</f>
+      </c>
+      <c r="AB15">
+        <f>AB13/X13</f>
+      </c>
+      <c r="AC15">
+        <f>AC13/Y13</f>
+      </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>13</v>
       </c>
@@ -1811,8 +1928,11 @@
       <c r="Y16">
         <v>7508</v>
       </c>
+      <c r="Z16">
+        <v>8563</v>
+      </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>9</v>
       </c>
@@ -1888,8 +2008,20 @@
       <c r="Y17">
         <f>Y16/Y$3</f>
       </c>
+      <c r="Z17">
+        <f>Z16/Z$3</f>
+      </c>
+      <c r="AA17">
+        <f>AA16/AA$3</f>
+      </c>
+      <c r="AB17">
+        <f>AB16/AB$3</f>
+      </c>
+      <c r="AC17">
+        <f>AC16/AC$3</f>
+      </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>7</v>
       </c>
@@ -1957,8 +2089,20 @@
       <c r="Y18">
         <f>Y16/U16-1</f>
       </c>
+      <c r="Z18">
+        <f>Z16/V16-1</f>
+      </c>
+      <c r="AA18">
+        <f>AA16/W16-1</f>
+      </c>
+      <c r="AB18">
+        <f>AB16/X16-1</f>
+      </c>
+      <c r="AC18">
+        <f>AC16/Y16-1</f>
+      </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
         <v>14</v>
       </c>
@@ -2034,8 +2178,11 @@
       <c r="Y19">
         <v>-639</v>
       </c>
+      <c r="Z19">
+        <v>-368</v>
+      </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>15</v>
       </c>
@@ -2111,8 +2258,11 @@
       <c r="Y20">
         <v>8518</v>
       </c>
+      <c r="Z20">
+        <v>7349</v>
+      </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>9</v>
       </c>
@@ -2188,8 +2338,11 @@
       <c r="Y21">
         <f>Y20/Y$3</f>
       </c>
+      <c r="Z21">
+        <f>Z20/Z$3</f>
+      </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>7</v>
       </c>
@@ -2257,8 +2410,20 @@
       <c r="Y22">
         <f>Y20/U20-1</f>
       </c>
+      <c r="Z22">
+        <f>Z20/V20-1</f>
+      </c>
+      <c r="AA22">
+        <f>AA20/W20-1</f>
+      </c>
+      <c r="AB22">
+        <f>AB20/X20-1</f>
+      </c>
+      <c r="AC22">
+        <f>AC20/Y20-1</f>
+      </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>16</v>
       </c>
@@ -2334,8 +2499,11 @@
       <c r="Y23">
         <v>1.74</v>
       </c>
+      <c r="Z23">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
         <v>17</v>
       </c>
@@ -2405,8 +2573,20 @@
       <c r="Y24">
         <f>Y26/SUM(V23:Y23)</f>
       </c>
+      <c r="Z24">
+        <f>Z26/SUM(W23:Z23)</f>
+      </c>
+      <c r="AA24">
+        <f>AA26/SUM(X23:AA23)</f>
+      </c>
+      <c r="AB24">
+        <f>AB26/SUM(Y23:AB23)</f>
+      </c>
+      <c r="AC24">
+        <f>AC26/SUM(Z23:AC23)</f>
+      </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
         <v>18</v>
       </c>
@@ -2470,8 +2650,20 @@
       <c r="Y25">
         <f>AVERAGE(V24:Y24)</f>
       </c>
+      <c r="Z25">
+        <f>AVERAGE(W24:Z24)</f>
+      </c>
+      <c r="AA25">
+        <f>AVERAGE(X24:AA24)</f>
+      </c>
+      <c r="AB25">
+        <f>AVERAGE(Y24:AB24)</f>
+      </c>
+      <c r="AC25">
+        <f>AVERAGE(Z24:AC24)</f>
+      </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
         <v>19</v>
       </c>
@@ -2546,6 +2738,9 @@
       </c>
       <c r="Y26">
         <v>369.63</v>
+      </c>
+      <c r="Z26">
+        <v>331.3</v>
       </c>
     </row>
   </sheetData>
